--- a/data/keywords/tracking-mots-cles.xlsx
+++ b/data/keywords/tracking-mots-cles.xlsx
@@ -40847,16 +40847,16 @@
         <v>5</v>
       </c>
       <c r="G1256" t="str">
-        <v/>
+        <v>/carburants-consommation/voiture-gpl-avantages-inconvenients</v>
       </c>
       <c r="H1256" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1256" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1256" t="str">
-        <v/>
+        <v>2026-09-04</v>
       </c>
     </row>
     <row r="1257">

--- a/data/keywords/tracking-mots-cles.xlsx
+++ b/data/keywords/tracking-mots-cles.xlsx
@@ -35989,10 +35989,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1104" t="str">
-        <v>à valider</v>
+        <v>publié</v>
       </c>
       <c r="J1104" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
     </row>
     <row r="1105">
@@ -36181,10 +36181,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1110" t="str">
-        <v>à valider</v>
+        <v>publié</v>
       </c>
       <c r="J1110" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
     </row>
     <row r="1111">
@@ -36405,10 +36405,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1117" t="str">
-        <v>à valider</v>
+        <v>publié</v>
       </c>
       <c r="J1117" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
     </row>
     <row r="1118">
@@ -36501,10 +36501,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1120" t="str">
-        <v>à valider</v>
+        <v>publié</v>
       </c>
       <c r="J1120" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
     </row>
     <row r="1121">
@@ -36629,10 +36629,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1124" t="str">
-        <v>à valider</v>
+        <v>publié</v>
       </c>
       <c r="J1124" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
     </row>
     <row r="1125">

--- a/data/keywords/tracking-mots-cles.xlsx
+++ b/data/keywords/tracking-mots-cles.xlsx
@@ -40751,16 +40751,16 @@
         <v>72414</v>
       </c>
       <c r="G1253" t="str">
-        <v/>
+        <v>/carburants-consommation/carburant-moins-cher-autour-de-moi</v>
       </c>
       <c r="H1253" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1253" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1253" t="str">
-        <v/>
+        <v>2026-09-04</v>
       </c>
     </row>
     <row r="1254">
@@ -40783,13 +40783,13 @@
         <v>60</v>
       </c>
       <c r="G1254" t="str">
-        <v/>
+        <v>/carburants-consommation/coffre-de-toit-consommation</v>
       </c>
       <c r="H1254" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1254" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1254" t="str">
         <v/>
@@ -40815,13 +40815,13 @@
         <v>5</v>
       </c>
       <c r="G1255" t="str">
-        <v/>
+        <v>/carburants-consommation/boitier-e85-homologue-prix</v>
       </c>
       <c r="H1255" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1255" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1255" t="str">
         <v/>
@@ -40879,13 +40879,13 @@
         <v>0</v>
       </c>
       <c r="G1257" t="str">
-        <v/>
+        <v>/carburants-consommation/prix-essence-evolution-2026</v>
       </c>
       <c r="H1257" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1257" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1257" t="str">
         <v/>
@@ -40911,13 +40911,13 @@
         <v>0</v>
       </c>
       <c r="G1258" t="str">
-        <v/>
+        <v>/carburants-consommation/stations-low-cost-qualite-carburant</v>
       </c>
       <c r="H1258" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1258" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1258" t="str">
         <v/>
@@ -40943,13 +40943,13 @@
         <v>0</v>
       </c>
       <c r="G1259" t="str">
-        <v/>
+        <v>/carburants-consommation/carte-carburant-particulier-cashback</v>
       </c>
       <c r="H1259" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1259" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1259" t="str">
         <v/>
@@ -41007,16 +41007,16 @@
         <v>0</v>
       </c>
       <c r="G1261" t="str">
-        <v/>
+        <v>/carburants-consommation/reprogrammation-e85-vs-boitier</v>
       </c>
       <c r="H1261" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1261" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1261" t="str">
-        <v/>
+        <v>2026-09-04</v>
       </c>
     </row>
     <row r="1262">
@@ -41039,13 +41039,13 @@
         <v>0</v>
       </c>
       <c r="G1262" t="str">
-        <v/>
+        <v>/carburants-consommation/e85-fiabilite-moteur-long-terme</v>
       </c>
       <c r="H1262" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1262" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1262" t="str">
         <v/>
@@ -41071,13 +41071,13 @@
         <v>0</v>
       </c>
       <c r="G1263" t="str">
-        <v/>
+        <v>/carburants-consommation/carte-grise-gratuite-e85</v>
       </c>
       <c r="H1263" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1263" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1263" t="str">
         <v/>
@@ -41103,13 +41103,13 @@
         <v>0</v>
       </c>
       <c r="G1264" t="str">
-        <v/>
+        <v>/carburants-consommation/gpl-reservoir-controle</v>
       </c>
       <c r="H1264" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1264" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1264" t="str">
         <v/>
@@ -41167,13 +41167,13 @@
         <v>0</v>
       </c>
       <c r="G1266" t="str">
-        <v/>
+        <v>/carburants-consommation/surconsommation-causes-courantes</v>
       </c>
       <c r="H1266" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1266" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1266" t="str">
         <v/>
@@ -41199,13 +41199,13 @@
         <v>0</v>
       </c>
       <c r="G1267" t="str">
-        <v/>
+        <v>/carburants-consommation/pneus-basse-resistance-economie</v>
       </c>
       <c r="H1267" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1267" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1267" t="str">
         <v/>
@@ -41231,13 +41231,13 @@
         <v>0</v>
       </c>
       <c r="G1268" t="str">
-        <v/>
+        <v>/carburants-consommation/climatisation-surconsommation</v>
       </c>
       <c r="H1268" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1268" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1268" t="str">
         <v/>

--- a/data/keywords/tracking-mots-cles.xlsx
+++ b/data/keywords/tracking-mots-cles.xlsx
@@ -35829,10 +35829,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1099" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1099" t="str">
-        <v/>
+        <v>2026-08-04</v>
       </c>
     </row>
     <row r="1100">
@@ -35861,10 +35861,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1100" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1100" t="str">
-        <v/>
+        <v>2026-08-04</v>
       </c>
     </row>
     <row r="1101">
@@ -35925,10 +35925,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1102" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1102" t="str">
-        <v/>
+        <v>2026-08-04</v>
       </c>
     </row>
     <row r="1103">
@@ -36245,10 +36245,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1112" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1112" t="str">
-        <v/>
+        <v>2026-08-04</v>
       </c>
     </row>
     <row r="1113">
@@ -36341,10 +36341,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1115" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1115" t="str">
-        <v/>
+        <v>2026-08-04</v>
       </c>
     </row>
     <row r="1116">
@@ -36373,10 +36373,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1116" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1116" t="str">
-        <v/>
+        <v>2026-08-05</v>
       </c>
     </row>
     <row r="1117">
@@ -36533,10 +36533,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1121" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1121" t="str">
-        <v/>
+        <v>2026-08-05</v>
       </c>
     </row>
     <row r="1122">
@@ -36565,10 +36565,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1122" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1122" t="str">
-        <v/>
+        <v>2026-08-05</v>
       </c>
     </row>
     <row r="1123">
@@ -36597,10 +36597,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1123" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1123" t="str">
-        <v/>
+        <v>2026-08-05</v>
       </c>
     </row>
     <row r="1124">
@@ -36661,10 +36661,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1125" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1125" t="str">
-        <v/>
+        <v>2026-08-05</v>
       </c>
     </row>
     <row r="1126">
@@ -36693,10 +36693,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1126" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1126" t="str">
-        <v/>
+        <v>2026-08-06</v>
       </c>
     </row>
     <row r="1127">
@@ -36757,10 +36757,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1128" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1128" t="str">
-        <v/>
+        <v>2026-08-06</v>
       </c>
     </row>
     <row r="1129">

--- a/data/keywords/tracking-mots-cles.xlsx
+++ b/data/keywords/tracking-mots-cles.xlsx
@@ -40975,13 +40975,13 @@
         <v>0</v>
       </c>
       <c r="G1260" t="str">
-        <v/>
+        <v>/carburants-consommation/e85-rentabilite-calcul</v>
       </c>
       <c r="H1260" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1260" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1260" t="str">
         <v/>
@@ -41263,16 +41263,16 @@
         <v>137672</v>
       </c>
       <c r="G1269" t="str">
-        <v/>
+        <v>/camping-car-van/limitation-vitesse-camping-car</v>
       </c>
       <c r="H1269" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1269" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1269" t="str">
-        <v/>
+        <v>2026-09-04</v>
       </c>
     </row>
     <row r="1270">
@@ -41295,13 +41295,13 @@
         <v>2120</v>
       </c>
       <c r="G1270" t="str">
-        <v/>
+        <v>/camping-car-van/peage-camping-car-classe</v>
       </c>
       <c r="H1270" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1270" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1270" t="str">
         <v/>
@@ -41327,13 +41327,13 @@
         <v>420</v>
       </c>
       <c r="G1271" t="str">
-        <v/>
+        <v>/camping-car-van/applications-aires-camping-car</v>
       </c>
       <c r="H1271" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1271" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1271" t="str">
         <v/>
@@ -41391,13 +41391,13 @@
         <v>0</v>
       </c>
       <c r="G1273" t="str">
-        <v/>
+        <v>/camping-car-van/profile-vs-integral-vs-capucine</v>
       </c>
       <c r="H1273" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1273" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1273" t="str">
         <v/>
@@ -41615,16 +41615,16 @@
         <v>0</v>
       </c>
       <c r="G1280" t="str">
-        <v/>
+        <v>/camping-car-van/aires-camping-car-gratuites-france</v>
       </c>
       <c r="H1280" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1280" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1280" t="str">
-        <v/>
+        <v>2026-09-04</v>
       </c>
     </row>
     <row r="1281">
@@ -41647,13 +41647,13 @@
         <v>0</v>
       </c>
       <c r="G1281" t="str">
-        <v/>
+        <v>/camping-car-van/france-passion-vignoble-etape</v>
       </c>
       <c r="H1281" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1281" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1281" t="str">
         <v/>
@@ -41679,13 +41679,13 @@
         <v>0</v>
       </c>
       <c r="G1282" t="str">
-        <v/>
+        <v>/camping-car-van/camping-car-hiver-ski-conseils</v>
       </c>
       <c r="H1282" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1282" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1282" t="str">
         <v/>
@@ -41871,13 +41871,13 @@
         <v>0</v>
       </c>
       <c r="G1288" t="str">
-        <v/>
+        <v>/camping-car-van/stationnement-camping-car-regles-ville</v>
       </c>
       <c r="H1288" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1288" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1288" t="str">
         <v/>

--- a/data/keywords/tracking-mots-cles.xlsx
+++ b/data/keywords/tracking-mots-cles.xlsx
@@ -41272,7 +41272,7 @@
         <v>programmé</v>
       </c>
       <c r="J1269" t="str">
-        <v>2026-09-04</v>
+        <v>2026-08-06</v>
       </c>
     </row>
     <row r="1270">
@@ -41397,10 +41397,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1273" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1273" t="str">
-        <v/>
+        <v>2026-08-06</v>
       </c>
     </row>
     <row r="1274">
@@ -41624,7 +41624,7 @@
         <v>programmé</v>
       </c>
       <c r="J1280" t="str">
-        <v>2026-09-04</v>
+        <v>2026-08-06</v>
       </c>
     </row>
     <row r="1281">

--- a/data/keywords/tracking-mots-cles.xlsx
+++ b/data/keywords/tracking-mots-cles.xlsx
@@ -36277,10 +36277,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1113" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1113" t="str">
-        <v/>
+        <v>2026-08-07</v>
       </c>
     </row>
     <row r="1114">
@@ -40981,10 +40981,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1260" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1260" t="str">
-        <v/>
+        <v>2026-08-07</v>
       </c>
     </row>
     <row r="1261">
@@ -41301,10 +41301,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1270" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1270" t="str">
-        <v/>
+        <v>2026-08-07</v>
       </c>
     </row>
     <row r="1271">
@@ -41333,10 +41333,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1271" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1271" t="str">
-        <v/>
+        <v>2026-08-07</v>
       </c>
     </row>
     <row r="1272">
@@ -41653,10 +41653,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1281" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1281" t="str">
-        <v/>
+        <v>2026-08-07</v>
       </c>
     </row>
     <row r="1282">
@@ -41685,10 +41685,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1282" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1282" t="str">
-        <v/>
+        <v>2026-08-08</v>
       </c>
     </row>
     <row r="1283">
@@ -41877,10 +41877,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1288" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1288" t="str">
-        <v/>
+        <v>2026-08-08</v>
       </c>
     </row>
     <row r="1289">

--- a/data/keywords/tracking-mots-cles.xlsx
+++ b/data/keywords/tracking-mots-cles.xlsx
@@ -40728,7 +40728,7 @@
         <v>programmé</v>
       </c>
       <c r="J1252" t="str">
-        <v>2026-09-04</v>
+        <v>2026-08-08</v>
       </c>
     </row>
     <row r="1253">
@@ -40760,7 +40760,7 @@
         <v>programmé</v>
       </c>
       <c r="J1253" t="str">
-        <v>2026-09-04</v>
+        <v>2026-08-08</v>
       </c>
     </row>
     <row r="1254">
@@ -40856,7 +40856,7 @@
         <v>programmé</v>
       </c>
       <c r="J1256" t="str">
-        <v>2026-09-04</v>
+        <v>2026-08-08</v>
       </c>
     </row>
     <row r="1257">
@@ -41016,7 +41016,7 @@
         <v>programmé</v>
       </c>
       <c r="J1261" t="str">
-        <v>2026-09-04</v>
+        <v>2026-08-09</v>
       </c>
     </row>
     <row r="1262">
@@ -41144,7 +41144,7 @@
         <v>programmé</v>
       </c>
       <c r="J1265" t="str">
-        <v>2026-09-04</v>
+        <v>2026-08-09</v>
       </c>
     </row>
     <row r="1266">

--- a/data/keywords/tracking-mots-cles.xlsx
+++ b/data/keywords/tracking-mots-cles.xlsx
@@ -41423,13 +41423,13 @@
         <v>0</v>
       </c>
       <c r="G1274" t="str">
-        <v/>
+        <v>/camping-car-van/camping-car-permis-b-poids</v>
       </c>
       <c r="H1274" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1274" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1274" t="str">
         <v/>
@@ -41455,16 +41455,16 @@
         <v>0</v>
       </c>
       <c r="G1275" t="str">
-        <v/>
+        <v>/camping-car-van/decote-camping-car-neuf</v>
       </c>
       <c r="H1275" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1275" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1275" t="str">
-        <v/>
+        <v>2026-08-05</v>
       </c>
     </row>
     <row r="1276">
@@ -41487,16 +41487,16 @@
         <v>0</v>
       </c>
       <c r="G1276" t="str">
-        <v/>
+        <v>/camping-car-van/van-amenage-occasion-choisir</v>
       </c>
       <c r="H1276" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1276" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1276" t="str">
-        <v/>
+        <v>2026-08-05</v>
       </c>
     </row>
     <row r="1277">
@@ -41519,16 +41519,16 @@
         <v>0</v>
       </c>
       <c r="G1277" t="str">
-        <v/>
+        <v>/camping-car-van/amenager-fourgon-soi-meme-homologation</v>
       </c>
       <c r="H1277" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1277" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1277" t="str">
-        <v/>
+        <v>2026-08-05</v>
       </c>
     </row>
     <row r="1278">
@@ -41551,13 +41551,13 @@
         <v>0</v>
       </c>
       <c r="G1278" t="str">
-        <v/>
+        <v>/camping-car-van/vasp-carte-grise-demarches</v>
       </c>
       <c r="H1278" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1278" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1278" t="str">
         <v/>
@@ -41583,16 +41583,16 @@
         <v>0</v>
       </c>
       <c r="G1279" t="str">
-        <v/>
+        <v>/camping-car-van/meilleur-fourgon-base-amenagement</v>
       </c>
       <c r="H1279" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1279" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1279" t="str">
-        <v/>
+        <v>2026-08-05</v>
       </c>
     </row>
     <row r="1280">
@@ -41711,16 +41711,16 @@
         <v>0</v>
       </c>
       <c r="G1283" t="str">
-        <v/>
+        <v>/camping-car-van/hivernage-camping-car-checklist</v>
       </c>
       <c r="H1283" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1283" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1283" t="str">
-        <v/>
+        <v>2026-08-06</v>
       </c>
     </row>
     <row r="1284">
@@ -41839,13 +41839,13 @@
         <v>0</v>
       </c>
       <c r="G1287" t="str">
-        <v/>
+        <v>/camping-car-van/assurance-camping-car-comparatif</v>
       </c>
       <c r="H1287" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1287" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1287" t="str">
         <v/>

--- a/data/keywords/tracking-mots-cles.xlsx
+++ b/data/keywords/tracking-mots-cles.xlsx
@@ -40079,13 +40079,13 @@
         <v>638625</v>
       </c>
       <c r="G1232" t="str">
-        <v/>
+        <v>/mobilite-partagee-transports/taxi-conventionne-cpam</v>
       </c>
       <c r="H1232" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1232" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1232" t="str">
         <v/>
@@ -41359,13 +41359,13 @@
         <v>0</v>
       </c>
       <c r="G1272" t="str">
-        <v/>
+        <v>/camping-car-van/camping-car-occasion-prix-conseils</v>
       </c>
       <c r="H1272" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1272" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1272" t="str">
         <v/>
@@ -41743,16 +41743,16 @@
         <v>0</v>
       </c>
       <c r="G1284" t="str">
-        <v/>
+        <v>/camping-car-van/etancheite-camping-car-controle</v>
       </c>
       <c r="H1284" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1284" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1284" t="str">
-        <v/>
+        <v>2026-08-06</v>
       </c>
     </row>
     <row r="1285">
@@ -41775,13 +41775,13 @@
         <v>0</v>
       </c>
       <c r="G1285" t="str">
-        <v/>
+        <v>/camping-car-van/batterie-cellule-entretien</v>
       </c>
       <c r="H1285" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1285" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1285" t="str">
         <v/>

--- a/data/keywords/tracking-mots-cles.xlsx
+++ b/data/keywords/tracking-mots-cles.xlsx
@@ -40143,13 +40143,13 @@
         <v>420</v>
       </c>
       <c r="G1234" t="str">
-        <v/>
+        <v>/mobilite-partagee-transports/prime-covoiturage-100-euros</v>
       </c>
       <c r="H1234" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1234" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1234" t="str">
         <v/>
@@ -40239,13 +40239,13 @@
         <v>20</v>
       </c>
       <c r="G1237" t="str">
-        <v/>
+        <v>/mobilite-partagee-transports/carte-vtc-examen</v>
       </c>
       <c r="H1237" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1237" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1237" t="str">
         <v/>
@@ -40559,13 +40559,13 @@
         <v>0</v>
       </c>
       <c r="G1247" t="str">
-        <v/>
+        <v>/mobilite-partagee-transports/devenir-chauffeur-vtc-conditions</v>
       </c>
       <c r="H1247" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1247" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1247" t="str">
         <v/>

--- a/data/keywords/tracking-mots-cles.xlsx
+++ b/data/keywords/tracking-mots-cles.xlsx
@@ -36053,10 +36053,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1106" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1106" t="str">
-        <v/>
+        <v>2026-08-14</v>
       </c>
     </row>
     <row r="1107">
@@ -36085,10 +36085,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1107" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1107" t="str">
-        <v/>
+        <v>2026-08-14</v>
       </c>
     </row>
     <row r="1108">
@@ -36117,10 +36117,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1108" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1108" t="str">
-        <v/>
+        <v>2026-08-15</v>
       </c>
     </row>
     <row r="1109">
@@ -36309,10 +36309,10 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1114" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1114" t="str">
-        <v/>
+        <v>2026-08-14</v>
       </c>
     </row>
     <row r="1115">
@@ -40085,10 +40085,10 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1232" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1232" t="str">
-        <v/>
+        <v>2026-08-12</v>
       </c>
     </row>
     <row r="1233">
@@ -40111,16 +40111,16 @@
         <v>70190</v>
       </c>
       <c r="G1233" t="str">
-        <v/>
+        <v>/mobilite-partagee-transports/blablacar-daily-avis</v>
       </c>
       <c r="H1233" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1233" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1233" t="str">
-        <v/>
+        <v>2026-08-11</v>
       </c>
     </row>
     <row r="1234">
@@ -40149,10 +40149,10 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1234" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1234" t="str">
-        <v/>
+        <v>2026-08-12</v>
       </c>
     </row>
     <row r="1235">
@@ -40175,16 +40175,16 @@
         <v>50</v>
       </c>
       <c r="G1235" t="str">
-        <v/>
+        <v>/mobilite-partagee-transports/ter-abonnement-travail</v>
       </c>
       <c r="H1235" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1235" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1235" t="str">
-        <v/>
+        <v>2026-08-14</v>
       </c>
     </row>
     <row r="1236">
@@ -40207,13 +40207,13 @@
         <v>24</v>
       </c>
       <c r="G1236" t="str">
-        <v/>
+        <v>/mobilite-partagee-transports/lld-particulier-sans-apport</v>
       </c>
       <c r="H1236" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1236" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1236" t="str">
         <v/>
@@ -40245,10 +40245,10 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1237" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1237" t="str">
-        <v/>
+        <v>2026-08-12</v>
       </c>
     </row>
     <row r="1238">
@@ -40271,16 +40271,16 @@
         <v>0</v>
       </c>
       <c r="G1238" t="str">
-        <v/>
+        <v>/mobilite-partagee-transports/covoiturage-domicile-travail-prime</v>
       </c>
       <c r="H1238" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1238" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1238" t="str">
-        <v/>
+        <v>2026-08-11</v>
       </c>
     </row>
     <row r="1239">
@@ -40303,13 +40303,13 @@
         <v>0</v>
       </c>
       <c r="G1239" t="str">
-        <v/>
+        <v>/mobilite-partagee-transports/covoiturage-courte-distance-applis</v>
       </c>
       <c r="H1239" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1239" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1239" t="str">
         <v/>
@@ -40335,16 +40335,16 @@
         <v>0</v>
       </c>
       <c r="G1240" t="str">
-        <v/>
+        <v>/mobilite-partagee-transports/location-voiture-entre-particuliers-avis</v>
       </c>
       <c r="H1240" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1240" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1240" t="str">
-        <v/>
+        <v>2026-08-12</v>
       </c>
     </row>
     <row r="1241">
@@ -40367,16 +40367,16 @@
         <v>0</v>
       </c>
       <c r="G1241" t="str">
-        <v/>
+        <v>/mobilite-partagee-transports/getaround-ouicar-comparatif</v>
       </c>
       <c r="H1241" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1241" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1241" t="str">
-        <v/>
+        <v>2026-08-13</v>
       </c>
     </row>
     <row r="1242">
@@ -40399,16 +40399,16 @@
         <v>0</v>
       </c>
       <c r="G1242" t="str">
-        <v/>
+        <v>/mobilite-partagee-transports/autopartage-citiz-tarifs</v>
       </c>
       <c r="H1242" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1242" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1242" t="str">
-        <v/>
+        <v>2026-08-13</v>
       </c>
     </row>
     <row r="1243">
@@ -40431,16 +40431,16 @@
         <v>0</v>
       </c>
       <c r="G1243" t="str">
-        <v/>
+        <v>/mobilite-partagee-transports/assurance-location-entre-particuliers</v>
       </c>
       <c r="H1243" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1243" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1243" t="str">
-        <v/>
+        <v>2026-08-13</v>
       </c>
     </row>
     <row r="1244">
@@ -40463,16 +40463,16 @@
         <v>0</v>
       </c>
       <c r="G1244" t="str">
-        <v/>
+        <v>/mobilite-partagee-transports/louer-voiture-pas-cher-week-end</v>
       </c>
       <c r="H1244" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1244" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1244" t="str">
-        <v/>
+        <v>2026-08-08</v>
       </c>
     </row>
     <row r="1245">
@@ -40495,16 +40495,16 @@
         <v>0</v>
       </c>
       <c r="G1245" t="str">
-        <v/>
+        <v>/mobilite-partagee-transports/location-voiture-aeroport-astuces</v>
       </c>
       <c r="H1245" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1245" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1245" t="str">
-        <v/>
+        <v>2026-08-11</v>
       </c>
     </row>
     <row r="1246">
@@ -40527,16 +40527,16 @@
         <v>0</v>
       </c>
       <c r="G1246" t="str">
-        <v/>
+        <v>/mobilite-partagee-transports/franchise-location-voiture-racheter</v>
       </c>
       <c r="H1246" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1246" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1246" t="str">
-        <v/>
+        <v>2026-08-11</v>
       </c>
     </row>
     <row r="1247">
@@ -40565,10 +40565,10 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1247" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1247" t="str">
-        <v/>
+        <v>2026-08-12</v>
       </c>
     </row>
     <row r="1248">
@@ -40591,16 +40591,16 @@
         <v>0</v>
       </c>
       <c r="G1248" t="str">
-        <v/>
+        <v>/mobilite-partagee-transports/uber-vs-bolt-comparatif-prix</v>
       </c>
       <c r="H1248" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1248" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1248" t="str">
-        <v/>
+        <v>2026-08-11</v>
       </c>
     </row>
     <row r="1249">
@@ -40623,16 +40623,16 @@
         <v>0</v>
       </c>
       <c r="G1249" t="str">
-        <v/>
+        <v>/mobilite-partagee-transports/carte-avantage-sncf-rentable</v>
       </c>
       <c r="H1249" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1249" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1249" t="str">
-        <v/>
+        <v>2026-08-13</v>
       </c>
     </row>
     <row r="1250">
@@ -40655,16 +40655,16 @@
         <v>0</v>
       </c>
       <c r="G1250" t="str">
-        <v/>
+        <v>/mobilite-partagee-transports/tgv-max-abonnement-avis</v>
       </c>
       <c r="H1250" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1250" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1250" t="str">
-        <v/>
+        <v>2026-08-14</v>
       </c>
     </row>
     <row r="1251">
@@ -40687,16 +40687,16 @@
         <v>0</v>
       </c>
       <c r="G1251" t="str">
-        <v/>
+        <v>/mobilite-partagee-transports/forfait-navigo-teletravail</v>
       </c>
       <c r="H1251" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1251" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1251" t="str">
-        <v/>
+        <v>2026-08-13</v>
       </c>
     </row>
     <row r="1252">
@@ -40917,10 +40917,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1258" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1258" t="str">
-        <v/>
+        <v>2026-08-15</v>
       </c>
     </row>
     <row r="1259">
@@ -41077,10 +41077,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1263" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1263" t="str">
-        <v/>
+        <v>2026-08-15</v>
       </c>
     </row>
     <row r="1264">
@@ -41109,10 +41109,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1264" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1264" t="str">
-        <v/>
+        <v>2026-08-15</v>
       </c>
     </row>
     <row r="1265">
@@ -41205,10 +41205,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1267" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1267" t="str">
-        <v/>
+        <v>2026-08-16</v>
       </c>
     </row>
     <row r="1268">
@@ -41237,10 +41237,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1268" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1268" t="str">
-        <v/>
+        <v>2026-08-15</v>
       </c>
     </row>
     <row r="1269">
@@ -41365,10 +41365,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1272" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1272" t="str">
-        <v/>
+        <v>2026-08-16</v>
       </c>
     </row>
     <row r="1273">
@@ -41429,10 +41429,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1274" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1274" t="str">
-        <v/>
+        <v>2026-08-16</v>
       </c>
     </row>
     <row r="1275">
@@ -41464,7 +41464,7 @@
         <v>programmé</v>
       </c>
       <c r="J1275" t="str">
-        <v>2026-08-05</v>
+        <v>2026-08-16</v>
       </c>
     </row>
     <row r="1276">
@@ -41496,7 +41496,7 @@
         <v>programmé</v>
       </c>
       <c r="J1276" t="str">
-        <v>2026-08-05</v>
+        <v>2026-08-17</v>
       </c>
     </row>
     <row r="1277">
@@ -41528,7 +41528,7 @@
         <v>programmé</v>
       </c>
       <c r="J1277" t="str">
-        <v>2026-08-05</v>
+        <v>2026-08-18</v>
       </c>
     </row>
     <row r="1278">
@@ -41557,10 +41557,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1278" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1278" t="str">
-        <v/>
+        <v>2026-08-17</v>
       </c>
     </row>
     <row r="1279">
@@ -41592,7 +41592,7 @@
         <v>programmé</v>
       </c>
       <c r="J1279" t="str">
-        <v>2026-08-05</v>
+        <v>2026-08-17</v>
       </c>
     </row>
     <row r="1280">
@@ -41720,7 +41720,7 @@
         <v>programmé</v>
       </c>
       <c r="J1283" t="str">
-        <v>2026-08-06</v>
+        <v>2026-08-17</v>
       </c>
     </row>
     <row r="1284">
@@ -41752,7 +41752,7 @@
         <v>programmé</v>
       </c>
       <c r="J1284" t="str">
-        <v>2026-08-06</v>
+        <v>2026-08-17</v>
       </c>
     </row>
     <row r="1285">
@@ -41781,10 +41781,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1285" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1285" t="str">
-        <v/>
+        <v>2026-08-16</v>
       </c>
     </row>
     <row r="1286">
@@ -41807,13 +41807,13 @@
         <v>0</v>
       </c>
       <c r="G1286" t="str">
-        <v/>
+        <v>/camping-car-van/gaz-camping-car-securite</v>
       </c>
       <c r="H1286" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1286" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1286" t="str">
         <v/>
@@ -41903,16 +41903,16 @@
         <v>133665</v>
       </c>
       <c r="G1289" t="str">
-        <v/>
+        <v>/utilitaires-flottes-pro/carte-carburant-pro-comparatif</v>
       </c>
       <c r="H1289" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1289" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1289" t="str">
-        <v/>
+        <v>2026-08-10</v>
       </c>
     </row>
     <row r="1290">
@@ -41935,13 +41935,13 @@
         <v>10223</v>
       </c>
       <c r="G1290" t="str">
-        <v/>
+        <v>/utilitaires-flottes-pro/meilleur-utilitaire-compact</v>
       </c>
       <c r="H1290" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1290" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1290" t="str">
         <v/>
@@ -42031,13 +42031,13 @@
         <v>0</v>
       </c>
       <c r="G1293" t="str">
-        <v/>
+        <v>/utilitaires-flottes-pro/pick-up-fiscalite-avantage</v>
       </c>
       <c r="H1293" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1293" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1293" t="str">
         <v/>
@@ -42095,16 +42095,16 @@
         <v>0</v>
       </c>
       <c r="G1295" t="str">
-        <v/>
+        <v>/utilitaires-flottes-pro/utilitaire-electrique-autonomie-reelle</v>
       </c>
       <c r="H1295" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1295" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1295" t="str">
-        <v/>
+        <v>2026-08-11</v>
       </c>
     </row>
     <row r="1296">
@@ -42223,13 +42223,13 @@
         <v>0</v>
       </c>
       <c r="G1299" t="str">
-        <v/>
+        <v>/utilitaires-flottes-pro/lld-utilitaire-pro-sans-apport</v>
       </c>
       <c r="H1299" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1299" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1299" t="str">
         <v/>
@@ -42255,16 +42255,16 @@
         <v>0</v>
       </c>
       <c r="G1300" t="str">
-        <v/>
+        <v>/utilitaires-flottes-pro/gestion-flotte-logiciel-tpe</v>
       </c>
       <c r="H1300" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1300" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1300" t="str">
-        <v/>
+        <v>2026-08-10</v>
       </c>
     </row>
     <row r="1301">
@@ -42287,13 +42287,13 @@
         <v>0</v>
       </c>
       <c r="G1301" t="str">
-        <v/>
+        <v>/utilitaires-flottes-pro/telematique-flotte-avantages</v>
       </c>
       <c r="H1301" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1301" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1301" t="str">
         <v/>
@@ -42351,16 +42351,16 @@
         <v>0</v>
       </c>
       <c r="G1303" t="str">
-        <v/>
+        <v>/utilitaires-flottes-pro/habillage-bois-utilitaire-kit</v>
       </c>
       <c r="H1303" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1303" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1303" t="str">
-        <v/>
+        <v>2026-08-11</v>
       </c>
     </row>
     <row r="1304">
@@ -42383,16 +42383,16 @@
         <v>0</v>
       </c>
       <c r="G1304" t="str">
-        <v/>
+        <v>/utilitaires-flottes-pro/attelage-utilitaire-homologation</v>
       </c>
       <c r="H1304" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1304" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1304" t="str">
-        <v/>
+        <v>2026-08-11</v>
       </c>
     </row>
     <row r="1305">
@@ -42511,13 +42511,13 @@
         <v>0</v>
       </c>
       <c r="G1308" t="str">
-        <v/>
+        <v>/utilitaires-flottes-pro/avantage-en-nature-vehicule-fonction</v>
       </c>
       <c r="H1308" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1308" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1308" t="str">
         <v/>

--- a/data/keywords/tracking-mots-cles.xlsx
+++ b/data/keywords/tracking-mots-cles.xlsx
@@ -35829,7 +35829,7 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1099" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1099" t="str">
         <v>2026-08-04</v>
@@ -35861,7 +35861,7 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1100" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1100" t="str">
         <v>2026-08-04</v>
@@ -35925,7 +35925,7 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1102" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1102" t="str">
         <v>2026-08-04</v>
@@ -36053,7 +36053,7 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1106" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1106" t="str">
         <v>2026-08-14</v>
@@ -36085,7 +36085,7 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1107" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1107" t="str">
         <v>2026-08-14</v>
@@ -36117,7 +36117,7 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1108" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1108" t="str">
         <v>2026-08-15</v>
@@ -36245,7 +36245,7 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1112" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1112" t="str">
         <v>2026-08-04</v>
@@ -36277,7 +36277,7 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1113" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1113" t="str">
         <v>2026-08-07</v>
@@ -36309,7 +36309,7 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1114" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1114" t="str">
         <v>2026-08-14</v>
@@ -36341,7 +36341,7 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1115" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1115" t="str">
         <v>2026-08-04</v>
@@ -36373,7 +36373,7 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1116" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1116" t="str">
         <v>2026-08-05</v>
@@ -36533,7 +36533,7 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1121" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1121" t="str">
         <v>2026-08-05</v>
@@ -36565,7 +36565,7 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1122" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1122" t="str">
         <v>2026-08-05</v>
@@ -36597,7 +36597,7 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1123" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1123" t="str">
         <v>2026-08-05</v>
@@ -36661,7 +36661,7 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1125" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1125" t="str">
         <v>2026-08-05</v>
@@ -36693,7 +36693,7 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1126" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1126" t="str">
         <v>2026-08-06</v>
@@ -36757,7 +36757,7 @@
         <v>D — Démarches, assurance &amp; permis</v>
       </c>
       <c r="I1128" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1128" t="str">
         <v>2026-08-06</v>
@@ -39407,16 +39407,16 @@
         <v>20083</v>
       </c>
       <c r="G1211" t="str">
-        <v/>
+        <v>/velo-nouvelles-mobilites/casque-trottinette-obligatoire</v>
       </c>
       <c r="H1211" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1211" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1211" t="str">
-        <v/>
+        <v>2026-08-25</v>
       </c>
     </row>
     <row r="1212">
@@ -39439,16 +39439,16 @@
         <v>11333</v>
       </c>
       <c r="G1212" t="str">
-        <v/>
+        <v>/velo-nouvelles-mobilites/leasing-velo-entreprise</v>
       </c>
       <c r="H1212" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1212" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1212" t="str">
-        <v/>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="1213">
@@ -39471,16 +39471,16 @@
         <v>145</v>
       </c>
       <c r="G1213" t="str">
-        <v/>
+        <v>/velo-nouvelles-mobilites/meilleure-trottinette-electrique</v>
       </c>
       <c r="H1213" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1213" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1213" t="str">
-        <v/>
+        <v>2026-08-25</v>
       </c>
     </row>
     <row r="1214">
@@ -39503,16 +39503,16 @@
         <v>9</v>
       </c>
       <c r="G1214" t="str">
-        <v/>
+        <v>/velo-nouvelles-mobilites/meilleur-eclairage-velo</v>
       </c>
       <c r="H1214" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1214" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1214" t="str">
-        <v/>
+        <v>2026-08-24</v>
       </c>
     </row>
     <row r="1215">
@@ -39535,16 +39535,16 @@
         <v>0</v>
       </c>
       <c r="G1215" t="str">
-        <v/>
+        <v>/velo-nouvelles-mobilites/meilleur-vae-2026</v>
       </c>
       <c r="H1215" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1215" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1215" t="str">
-        <v/>
+        <v>2026-08-26</v>
       </c>
     </row>
     <row r="1216">
@@ -39567,13 +39567,13 @@
         <v>0</v>
       </c>
       <c r="G1216" t="str">
-        <v/>
+        <v>/velo-nouvelles-mobilites/vae-ville-confort-comparatif</v>
       </c>
       <c r="H1216" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1216" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1216" t="str">
         <v/>
@@ -39631,16 +39631,16 @@
         <v>0</v>
       </c>
       <c r="G1218" t="str">
-        <v/>
+        <v>/velo-nouvelles-mobilites/batterie-vae-duree-de-vie</v>
       </c>
       <c r="H1218" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1218" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1218" t="str">
-        <v/>
+        <v>2026-08-26</v>
       </c>
     </row>
     <row r="1219">
@@ -39695,16 +39695,16 @@
         <v>0</v>
       </c>
       <c r="G1220" t="str">
-        <v/>
+        <v>/velo-nouvelles-mobilites/trottinette-electrique-autonomie-reelle</v>
       </c>
       <c r="H1220" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1220" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1220" t="str">
-        <v/>
+        <v>2026-08-25</v>
       </c>
     </row>
     <row r="1221">
@@ -39727,16 +39727,16 @@
         <v>0</v>
       </c>
       <c r="G1221" t="str">
-        <v/>
+        <v>/velo-nouvelles-mobilites/reglementation-edpm-2026</v>
       </c>
       <c r="H1221" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1221" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1221" t="str">
-        <v/>
+        <v>2026-08-25</v>
       </c>
     </row>
     <row r="1222">
@@ -39759,16 +39759,16 @@
         <v>0</v>
       </c>
       <c r="G1222" t="str">
-        <v/>
+        <v>/velo-nouvelles-mobilites/prime-velo-electrique-2026</v>
       </c>
       <c r="H1222" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1222" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1222" t="str">
-        <v/>
+        <v>2026-08-24</v>
       </c>
     </row>
     <row r="1223">
@@ -39791,16 +39791,16 @@
         <v>0</v>
       </c>
       <c r="G1223" t="str">
-        <v/>
+        <v>/velo-nouvelles-mobilites/aide-locale-achat-vae</v>
       </c>
       <c r="H1223" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1223" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1223" t="str">
-        <v/>
+        <v>2026-08-24</v>
       </c>
     </row>
     <row r="1224">
@@ -39823,16 +39823,16 @@
         <v>0</v>
       </c>
       <c r="G1224" t="str">
-        <v/>
+        <v>/velo-nouvelles-mobilites/forfait-mobilites-durables-velo</v>
       </c>
       <c r="H1224" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1224" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1224" t="str">
-        <v/>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="1225">
@@ -39855,16 +39855,16 @@
         <v>0</v>
       </c>
       <c r="G1225" t="str">
-        <v/>
+        <v>/velo-nouvelles-mobilites/antivol-velo-u-comparatif</v>
       </c>
       <c r="H1225" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1225" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1225" t="str">
-        <v/>
+        <v>2026-08-24</v>
       </c>
     </row>
     <row r="1226">
@@ -39887,16 +39887,16 @@
         <v>0</v>
       </c>
       <c r="G1226" t="str">
-        <v/>
+        <v>/velo-nouvelles-mobilites/traceur-gps-velo-cache</v>
       </c>
       <c r="H1226" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1226" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1226" t="str">
-        <v/>
+        <v>2026-08-24</v>
       </c>
     </row>
     <row r="1227">
@@ -39919,16 +39919,16 @@
         <v>0</v>
       </c>
       <c r="G1227" t="str">
-        <v/>
+        <v>/velo-nouvelles-mobilites/marquage-bicycode-obligatoire</v>
       </c>
       <c r="H1227" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1227" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1227" t="str">
-        <v/>
+        <v>2026-08-25</v>
       </c>
     </row>
     <row r="1228">
@@ -39951,13 +39951,13 @@
         <v>0</v>
       </c>
       <c r="G1228" t="str">
-        <v/>
+        <v>/velo-nouvelles-mobilites/velotaf-debuter-conseils</v>
       </c>
       <c r="H1228" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1228" t="str">
-        <v>à faire</v>
+        <v>à valider</v>
       </c>
       <c r="J1228" t="str">
         <v/>
@@ -39983,16 +39983,16 @@
         <v>0</v>
       </c>
       <c r="G1229" t="str">
-        <v/>
+        <v>/velo-nouvelles-mobilites/itineraire-velo-securise-appli</v>
       </c>
       <c r="H1229" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1229" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1229" t="str">
-        <v/>
+        <v>2026-08-26</v>
       </c>
     </row>
     <row r="1230">
@@ -40015,16 +40015,16 @@
         <v>0</v>
       </c>
       <c r="G1230" t="str">
-        <v/>
+        <v>/velo-nouvelles-mobilites/velo-pliant-train-comparatif</v>
       </c>
       <c r="H1230" t="str">
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1230" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1230" t="str">
-        <v/>
+        <v>2026-08-26</v>
       </c>
     </row>
     <row r="1231">
@@ -40085,7 +40085,7 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1232" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1232" t="str">
         <v>2026-08-12</v>
@@ -40117,7 +40117,7 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1233" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1233" t="str">
         <v>2026-08-11</v>
@@ -40149,7 +40149,7 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1234" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1234" t="str">
         <v>2026-08-12</v>
@@ -40181,7 +40181,7 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1235" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1235" t="str">
         <v>2026-08-14</v>
@@ -40213,10 +40213,10 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1236" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1236" t="str">
-        <v/>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="1237">
@@ -40245,7 +40245,7 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1237" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1237" t="str">
         <v>2026-08-12</v>
@@ -40277,7 +40277,7 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1238" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1238" t="str">
         <v>2026-08-11</v>
@@ -40309,10 +40309,10 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1239" t="str">
-        <v>à valider</v>
+        <v>publié</v>
       </c>
       <c r="J1239" t="str">
-        <v/>
+        <v>2026-08-10</v>
       </c>
     </row>
     <row r="1240">
@@ -40341,7 +40341,7 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1240" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1240" t="str">
         <v>2026-08-12</v>
@@ -40373,7 +40373,7 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1241" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1241" t="str">
         <v>2026-08-13</v>
@@ -40405,7 +40405,7 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1242" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1242" t="str">
         <v>2026-08-13</v>
@@ -40437,7 +40437,7 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1243" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1243" t="str">
         <v>2026-08-13</v>
@@ -40472,7 +40472,7 @@
         <v>programmé</v>
       </c>
       <c r="J1244" t="str">
-        <v>2026-08-08</v>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="1245">
@@ -40501,7 +40501,7 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1245" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1245" t="str">
         <v>2026-08-11</v>
@@ -40533,7 +40533,7 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1246" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1246" t="str">
         <v>2026-08-11</v>
@@ -40565,7 +40565,7 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1247" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1247" t="str">
         <v>2026-08-12</v>
@@ -40597,7 +40597,7 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1248" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1248" t="str">
         <v>2026-08-11</v>
@@ -40629,7 +40629,7 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1249" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1249" t="str">
         <v>2026-08-13</v>
@@ -40661,7 +40661,7 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1250" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1250" t="str">
         <v>2026-08-14</v>
@@ -40693,7 +40693,7 @@
         <v>E — Deux-roues &amp; nouvelles mobilités</v>
       </c>
       <c r="I1251" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1251" t="str">
         <v>2026-08-13</v>
@@ -40725,7 +40725,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1252" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1252" t="str">
         <v>2026-08-08</v>
@@ -40757,7 +40757,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1253" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1253" t="str">
         <v>2026-08-08</v>
@@ -40789,10 +40789,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1254" t="str">
-        <v>à valider</v>
+        <v>publié</v>
       </c>
       <c r="J1254" t="str">
-        <v/>
+        <v>2026-08-09</v>
       </c>
     </row>
     <row r="1255">
@@ -40821,10 +40821,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1255" t="str">
-        <v>à valider</v>
+        <v>publié</v>
       </c>
       <c r="J1255" t="str">
-        <v/>
+        <v>2026-08-09</v>
       </c>
     </row>
     <row r="1256">
@@ -40853,7 +40853,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1256" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1256" t="str">
         <v>2026-08-08</v>
@@ -40885,10 +40885,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1257" t="str">
-        <v>à valider</v>
+        <v>publié</v>
       </c>
       <c r="J1257" t="str">
-        <v/>
+        <v>2026-08-09</v>
       </c>
     </row>
     <row r="1258">
@@ -40917,7 +40917,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1258" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1258" t="str">
         <v>2026-08-15</v>
@@ -40949,10 +40949,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1259" t="str">
-        <v>à valider</v>
+        <v>publié</v>
       </c>
       <c r="J1259" t="str">
-        <v/>
+        <v>2026-08-10</v>
       </c>
     </row>
     <row r="1260">
@@ -40981,7 +40981,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1260" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1260" t="str">
         <v>2026-08-07</v>
@@ -41013,7 +41013,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1261" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1261" t="str">
         <v>2026-08-09</v>
@@ -41045,10 +41045,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1262" t="str">
-        <v>à valider</v>
+        <v>publié</v>
       </c>
       <c r="J1262" t="str">
-        <v/>
+        <v>2026-08-10</v>
       </c>
     </row>
     <row r="1263">
@@ -41077,7 +41077,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1263" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1263" t="str">
         <v>2026-08-15</v>
@@ -41109,7 +41109,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1264" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1264" t="str">
         <v>2026-08-15</v>
@@ -41141,7 +41141,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1265" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1265" t="str">
         <v>2026-08-09</v>
@@ -41173,10 +41173,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1266" t="str">
-        <v>à valider</v>
+        <v>publié</v>
       </c>
       <c r="J1266" t="str">
-        <v/>
+        <v>2026-08-10</v>
       </c>
     </row>
     <row r="1267">
@@ -41205,7 +41205,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1267" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1267" t="str">
         <v>2026-08-16</v>
@@ -41237,7 +41237,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1268" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1268" t="str">
         <v>2026-08-15</v>
@@ -41269,7 +41269,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1269" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1269" t="str">
         <v>2026-08-06</v>
@@ -41301,7 +41301,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1270" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1270" t="str">
         <v>2026-08-07</v>
@@ -41333,7 +41333,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1271" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1271" t="str">
         <v>2026-08-07</v>
@@ -41365,7 +41365,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1272" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1272" t="str">
         <v>2026-08-16</v>
@@ -41397,7 +41397,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1273" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1273" t="str">
         <v>2026-08-06</v>
@@ -41429,7 +41429,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1274" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1274" t="str">
         <v>2026-08-16</v>
@@ -41461,7 +41461,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1275" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1275" t="str">
         <v>2026-08-16</v>
@@ -41493,7 +41493,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1276" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1276" t="str">
         <v>2026-08-17</v>
@@ -41557,7 +41557,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1278" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1278" t="str">
         <v>2026-08-17</v>
@@ -41589,7 +41589,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1279" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1279" t="str">
         <v>2026-08-17</v>
@@ -41621,7 +41621,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1280" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1280" t="str">
         <v>2026-08-06</v>
@@ -41653,7 +41653,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1281" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1281" t="str">
         <v>2026-08-07</v>
@@ -41685,7 +41685,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1282" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1282" t="str">
         <v>2026-08-08</v>
@@ -41717,7 +41717,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1283" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1283" t="str">
         <v>2026-08-17</v>
@@ -41749,7 +41749,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1284" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1284" t="str">
         <v>2026-08-17</v>
@@ -41781,7 +41781,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1285" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1285" t="str">
         <v>2026-08-16</v>
@@ -41813,10 +41813,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1286" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1286" t="str">
-        <v/>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="1287">
@@ -41845,10 +41845,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1287" t="str">
-        <v>à valider</v>
+        <v>publié</v>
       </c>
       <c r="J1287" t="str">
-        <v/>
+        <v>2026-08-10</v>
       </c>
     </row>
     <row r="1288">
@@ -41877,7 +41877,7 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1288" t="str">
-        <v>programmé</v>
+        <v>publié</v>
       </c>
       <c r="J1288" t="str">
         <v>2026-08-08</v>
@@ -41912,7 +41912,7 @@
         <v>programmé</v>
       </c>
       <c r="J1289" t="str">
-        <v>2026-08-10</v>
+        <v>2026-08-21</v>
       </c>
     </row>
     <row r="1290">
@@ -41941,10 +41941,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1290" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1290" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
     </row>
     <row r="1291">
@@ -41967,16 +41967,16 @@
         <v>2535</v>
       </c>
       <c r="G1291" t="str">
-        <v/>
+        <v>/utilitaires-flottes-pro/amenagement-utilitaire-artisan</v>
       </c>
       <c r="H1291" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1291" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1291" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
     </row>
     <row r="1292">
@@ -41999,16 +41999,16 @@
         <v>0</v>
       </c>
       <c r="G1292" t="str">
-        <v/>
+        <v>/utilitaires-flottes-pro/fourgon-3m3-vs-6m3-usages</v>
       </c>
       <c r="H1292" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1292" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1292" t="str">
-        <v/>
+        <v>2026-08-20</v>
       </c>
     </row>
     <row r="1293">
@@ -42037,10 +42037,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1293" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1293" t="str">
-        <v/>
+        <v>2026-08-20</v>
       </c>
     </row>
     <row r="1294">
@@ -42063,16 +42063,16 @@
         <v>0</v>
       </c>
       <c r="G1294" t="str">
-        <v/>
+        <v>/utilitaires-flottes-pro/utilitaire-occasion-kilometrage</v>
       </c>
       <c r="H1294" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1294" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1294" t="str">
-        <v/>
+        <v>2026-08-20</v>
       </c>
     </row>
     <row r="1295">
@@ -42104,7 +42104,7 @@
         <v>programmé</v>
       </c>
       <c r="J1295" t="str">
-        <v>2026-08-11</v>
+        <v>2026-08-22</v>
       </c>
     </row>
     <row r="1296">
@@ -42127,16 +42127,16 @@
         <v>0</v>
       </c>
       <c r="G1296" t="str">
-        <v/>
+        <v>/utilitaires-flottes-pro/aides-utilitaire-electrique-pro</v>
       </c>
       <c r="H1296" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1296" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1296" t="str">
-        <v/>
+        <v>2026-08-22</v>
       </c>
     </row>
     <row r="1297">
@@ -42159,16 +42159,16 @@
         <v>0</v>
       </c>
       <c r="G1297" t="str">
-        <v/>
+        <v>/utilitaires-flottes-pro/recharge-flotte-entreprise</v>
       </c>
       <c r="H1297" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1297" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1297" t="str">
-        <v/>
+        <v>2026-08-22</v>
       </c>
     </row>
     <row r="1298">
@@ -42191,16 +42191,16 @@
         <v>0</v>
       </c>
       <c r="G1298" t="str">
-        <v/>
+        <v>/utilitaires-flottes-pro/kangoo-master-electrique-avis</v>
       </c>
       <c r="H1298" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1298" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1298" t="str">
-        <v/>
+        <v>2026-08-22</v>
       </c>
     </row>
     <row r="1299">
@@ -42229,10 +42229,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1299" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1299" t="str">
-        <v/>
+        <v>2026-08-21</v>
       </c>
     </row>
     <row r="1300">
@@ -42264,7 +42264,7 @@
         <v>programmé</v>
       </c>
       <c r="J1300" t="str">
-        <v>2026-08-10</v>
+        <v>2026-08-21</v>
       </c>
     </row>
     <row r="1301">
@@ -42293,10 +42293,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1301" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1301" t="str">
-        <v/>
+        <v>2026-08-22</v>
       </c>
     </row>
     <row r="1302">
@@ -42319,16 +42319,16 @@
         <v>0</v>
       </c>
       <c r="G1302" t="str">
-        <v/>
+        <v>/utilitaires-flottes-pro/galerie-et-porte-echelle-fourgon</v>
       </c>
       <c r="H1302" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1302" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1302" t="str">
-        <v/>
+        <v>2026-08-19</v>
       </c>
     </row>
     <row r="1303">
@@ -42360,7 +42360,7 @@
         <v>programmé</v>
       </c>
       <c r="J1303" t="str">
-        <v>2026-08-11</v>
+        <v>2026-08-19</v>
       </c>
     </row>
     <row r="1304">
@@ -42392,7 +42392,7 @@
         <v>programmé</v>
       </c>
       <c r="J1304" t="str">
-        <v>2026-08-11</v>
+        <v>2026-08-19</v>
       </c>
     </row>
     <row r="1305">
@@ -42415,16 +42415,16 @@
         <v>0</v>
       </c>
       <c r="G1305" t="str">
-        <v/>
+        <v>/utilitaires-flottes-pro/tvs-taxe-vehicules-societe-calcul</v>
       </c>
       <c r="H1305" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1305" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1305" t="str">
-        <v/>
+        <v>2026-08-21</v>
       </c>
     </row>
     <row r="1306">
@@ -42447,16 +42447,16 @@
         <v>0</v>
       </c>
       <c r="G1306" t="str">
-        <v/>
+        <v>/utilitaires-flottes-pro/tva-recuperable-utilitaire</v>
       </c>
       <c r="H1306" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1306" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1306" t="str">
-        <v/>
+        <v>2026-08-20</v>
       </c>
     </row>
     <row r="1307">
@@ -42479,16 +42479,16 @@
         <v>0</v>
       </c>
       <c r="G1307" t="str">
-        <v/>
+        <v>/utilitaires-flottes-pro/amortissement-vehicule-societe-plafond</v>
       </c>
       <c r="H1307" t="str">
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1307" t="str">
-        <v>à faire</v>
+        <v>programmé</v>
       </c>
       <c r="J1307" t="str">
-        <v/>
+        <v>2026-08-20</v>
       </c>
     </row>
     <row r="1308">
@@ -42517,10 +42517,10 @@
         <v>F — Usages spécifiques &amp; voyage</v>
       </c>
       <c r="I1308" t="str">
-        <v>à valider</v>
+        <v>programmé</v>
       </c>
       <c r="J1308" t="str">
-        <v/>
+        <v>2026-08-21</v>
       </c>
     </row>
     <row r="1309">

--- a/data/keywords/tracking-mots-cles.xlsx
+++ b/data/keywords/tracking-mots-cles.xlsx
@@ -37333,6 +37333,9 @@
       <c r="K965" t="str">
         <v>à valider</v>
       </c>
+      <c r="L965" t="str">
+        <v/>
+      </c>
     </row>
     <row r="966">
       <c r="A966" t="str">
@@ -37482,6 +37485,9 @@
       <c r="K969" t="str">
         <v>à valider</v>
       </c>
+      <c r="L969" t="str">
+        <v/>
+      </c>
     </row>
     <row r="970">
       <c r="A970" t="str">
@@ -37517,6 +37523,9 @@
       <c r="K970" t="str">
         <v>à valider</v>
       </c>
+      <c r="L970" t="str">
+        <v/>
+      </c>
     </row>
     <row r="971">
       <c r="A971" t="str">
@@ -37742,6 +37751,9 @@
       <c r="K976" t="str">
         <v>à valider</v>
       </c>
+      <c r="L976" t="str">
+        <v/>
+      </c>
     </row>
     <row r="977">
       <c r="A977" t="str">
@@ -37777,6 +37789,9 @@
       <c r="K977" t="str">
         <v>à valider</v>
       </c>
+      <c r="L977" t="str">
+        <v/>
+      </c>
     </row>
     <row r="978">
       <c r="A978" t="str">
@@ -37812,6 +37827,9 @@
       <c r="K978" t="str">
         <v>à valider</v>
       </c>
+      <c r="L978" t="str">
+        <v/>
+      </c>
     </row>
     <row r="979">
       <c r="A979" t="str">
@@ -42551,7 +42569,7 @@
         <v>666.5</v>
       </c>
       <c r="I1103" t="str">
-        <v>/carte-grise-demarches/changement-de-titulaire-carte-grise</v>
+        <v>/carte-grise-demarches/changement-de-titulaire</v>
       </c>
       <c r="J1103" t="str">
         <v>D — Démarches, assurance &amp; permis</v>
@@ -42627,7 +42645,7 @@
         <v>332.56</v>
       </c>
       <c r="I1105" t="str">
-        <v>/carte-grise-demarches/changement-adresse-carte-grise-gratuit</v>
+        <v>/carte-grise-demarches/changement-d-adresse-sur-la-carte-grise</v>
       </c>
       <c r="J1105" t="str">
         <v>D — Démarches, assurance &amp; permis</v>
@@ -42817,7 +42835,7 @@
         <v>0</v>
       </c>
       <c r="I1110" t="str">
-        <v>/carte-grise-demarches/changement-titulaire-carte-grise-en-ligne</v>
+        <v>/carte-grise-demarches/changement-de-titulaire</v>
       </c>
       <c r="J1110" t="str">
         <v>D — Démarches, assurance &amp; permis</v>
@@ -46663,6 +46681,9 @@
       <c r="K1211" t="str">
         <v>à valider</v>
       </c>
+      <c r="L1211" t="str">
+        <v/>
+      </c>
     </row>
     <row r="1212">
       <c r="A1212" t="str">
@@ -46888,6 +46909,9 @@
       <c r="K1217" t="str">
         <v>à valider</v>
       </c>
+      <c r="L1217" t="str">
+        <v/>
+      </c>
     </row>
     <row r="1218">
       <c r="A1218" t="str">
@@ -46961,6 +46985,9 @@
       <c r="K1219" t="str">
         <v>à valider</v>
       </c>
+      <c r="L1219" t="str">
+        <v/>
+      </c>
     </row>
     <row r="1220">
       <c r="A1220" t="str">
@@ -47413,6 +47440,9 @@
       </c>
       <c r="K1231" t="str">
         <v>à valider</v>
+      </c>
+      <c r="L1231" t="str">
+        <v/>
       </c>
     </row>
     <row r="1232">

--- a/data/keywords/tracking-mots-cles.xlsx
+++ b/data/keywords/tracking-mots-cles.xlsx
@@ -43253,7 +43253,7 @@
         <v>0</v>
       </c>
       <c r="I1121" t="str">
-        <v>/carte-grise-demarches/calcul-malus-occasion-importee</v>
+        <v>/carte-grise-demarches/taxe-co2-vehicule-occasion</v>
       </c>
       <c r="J1121" t="str">
         <v>D — Démarches, assurance &amp; permis</v>
@@ -43329,7 +43329,7 @@
         <v>0</v>
       </c>
       <c r="I1123" t="str">
-        <v>/carte-grise-demarches/cheval-fiscal-prix-par-region</v>
+        <v>/carte-grise-demarches/carte-grise-prix-par-region</v>
       </c>
       <c r="J1123" t="str">
         <v>D — Démarches, assurance &amp; permis</v>
